--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H514"/>
+  <dimension ref="A1:H516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15852,6 +15852,66 @@
         <v>331.12</v>
       </c>
       <c r="H514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>322.15</v>
+      </c>
+      <c r="C515" t="n">
+        <v>329.6</v>
+      </c>
+      <c r="D515" t="n">
+        <v>332.62</v>
+      </c>
+      <c r="E515" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="F515" t="n">
+        <v>332.8</v>
+      </c>
+      <c r="G515" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:20+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>321.73</v>
+      </c>
+      <c r="C516" t="n">
+        <v>329.35</v>
+      </c>
+      <c r="D516" t="n">
+        <v>332.62</v>
+      </c>
+      <c r="E516" t="n">
+        <v>335.41</v>
+      </c>
+      <c r="F516" t="n">
+        <v>332.56</v>
+      </c>
+      <c r="G516" t="n">
+        <v>331.31</v>
+      </c>
+      <c r="H516" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15868,7 +15928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B547"/>
+  <dimension ref="A1:B549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21341,6 +21401,26 @@
       </c>
       <c r="B547" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -21509,28 +21589,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.57741082006339</v>
+        <v>-2.573973013476023</v>
       </c>
       <c r="J2" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K2" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8935413035951624</v>
+        <v>0.8938260744542753</v>
       </c>
       <c r="M2" t="n">
-        <v>5.334079458840796</v>
+        <v>5.333977337516006</v>
       </c>
       <c r="N2" t="n">
-        <v>47.3581397343314</v>
+        <v>47.26701817134761</v>
       </c>
       <c r="O2" t="n">
-        <v>6.881725055124726</v>
+        <v>6.875101320805942</v>
       </c>
       <c r="P2" t="n">
-        <v>386.433221519054</v>
+        <v>386.3969274065884</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21587,28 +21667,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.371504909690358</v>
+        <v>-2.365294523949805</v>
       </c>
       <c r="J3" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K3" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9115340869442243</v>
+        <v>0.9109788871919831</v>
       </c>
       <c r="M3" t="n">
-        <v>4.539884824035653</v>
+        <v>4.559258141589329</v>
       </c>
       <c r="N3" t="n">
-        <v>32.65968073696742</v>
+        <v>32.83526546262826</v>
       </c>
       <c r="O3" t="n">
-        <v>5.714864892275882</v>
+        <v>5.730206406633906</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4606223384617</v>
+        <v>384.3950562343617</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21665,28 +21745,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.191948187673286</v>
+        <v>-2.188167233804795</v>
       </c>
       <c r="J4" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K4" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9193350715425107</v>
+        <v>0.9193149304887456</v>
       </c>
       <c r="M4" t="n">
-        <v>3.72198188434237</v>
+        <v>3.730781446944583</v>
       </c>
       <c r="N4" t="n">
-        <v>25.22506660407858</v>
+        <v>25.23918094168982</v>
       </c>
       <c r="O4" t="n">
-        <v>5.022456232171524</v>
+        <v>5.023861158679629</v>
       </c>
       <c r="P4" t="n">
-        <v>386.2450622575441</v>
+        <v>386.2051445445211</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21743,28 +21823,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.129692164230882</v>
+        <v>-2.125849975212372</v>
       </c>
       <c r="J5" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K5" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9337828378483414</v>
+        <v>0.9336588808381172</v>
       </c>
       <c r="M5" t="n">
-        <v>3.162432575505531</v>
+        <v>3.170646185571604</v>
       </c>
       <c r="N5" t="n">
-        <v>19.24505564129835</v>
+        <v>19.28613303114364</v>
       </c>
       <c r="O5" t="n">
-        <v>4.386918695542276</v>
+        <v>4.39159800427403</v>
       </c>
       <c r="P5" t="n">
-        <v>387.4362621554013</v>
+        <v>387.3956985752966</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21821,28 +21901,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.101127298752532</v>
+        <v>-2.098100306819812</v>
       </c>
       <c r="J6" t="n">
+        <v>515</v>
+      </c>
+      <c r="K6" t="n">
         <v>513</v>
       </c>
-      <c r="K6" t="n">
-        <v>511</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.9344386730673052</v>
+        <v>0.9344952903338324</v>
       </c>
       <c r="M6" t="n">
-        <v>3.17881975026157</v>
+        <v>3.185711609787253</v>
       </c>
       <c r="N6" t="n">
-        <v>18.29258083115342</v>
+        <v>18.29182343536037</v>
       </c>
       <c r="O6" t="n">
-        <v>4.276982678378932</v>
+        <v>4.276894134224083</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9849935377626</v>
+        <v>384.9527248959201</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21899,28 +21979,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.900134719322214</v>
+        <v>-1.899227672687966</v>
       </c>
       <c r="J7" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9324352845548092</v>
+        <v>0.932828220155652</v>
       </c>
       <c r="M7" t="n">
-        <v>2.804761853561986</v>
+        <v>2.799250874552045</v>
       </c>
       <c r="N7" t="n">
-        <v>15.67388147422928</v>
+        <v>15.61938031765035</v>
       </c>
       <c r="O7" t="n">
-        <v>3.959025318715363</v>
+        <v>3.952136171445811</v>
       </c>
       <c r="P7" t="n">
-        <v>381.2773234315349</v>
+        <v>381.2677497896391</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21958,7 +22038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H514"/>
+  <dimension ref="A1:H516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43537,6 +43617,90 @@
         </is>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-41.15358311217028,176.02773307866036</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-41.153929062001396,176.0269583214012</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-41.15423928191679,176.02616014296376</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-41.154550307276004,176.0253624929787</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-41.154812455807374,176.0245328050329</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-41.15508783007651,176.02371178753089</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:20+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-41.153579724786375,176.02773085816523</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-41.15392704569516,176.02695699968527</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-41.15423928191679,176.02616014296376</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-41.15454764573431,176.02536074833708</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-41.154810520133914,176.02453153621306</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-41.15508629766308,176.02371078305637</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H516"/>
+  <dimension ref="A1:H519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15912,6 +15912,96 @@
         <v>331.31</v>
       </c>
       <c r="H516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>321.44</v>
+      </c>
+      <c r="C517" t="n">
+        <v>329.63</v>
+      </c>
+      <c r="D517" t="n">
+        <v>332.74</v>
+      </c>
+      <c r="E517" t="n">
+        <v>335.73</v>
+      </c>
+      <c r="F517" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="G517" t="n">
+        <v>330.7</v>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>321.39</v>
+      </c>
+      <c r="C518" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D518" t="n">
+        <v>333.12</v>
+      </c>
+      <c r="E518" t="n">
+        <v>335.91</v>
+      </c>
+      <c r="F518" t="n">
+        <v>331.77</v>
+      </c>
+      <c r="G518" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="C519" t="n">
+        <v>330.23</v>
+      </c>
+      <c r="D519" t="n">
+        <v>333.67</v>
+      </c>
+      <c r="E519" t="n">
+        <v>336.22</v>
+      </c>
+      <c r="F519" t="n">
+        <v>332.09</v>
+      </c>
+      <c r="G519" t="n">
+        <v>330.85</v>
+      </c>
+      <c r="H519" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -15928,7 +16018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B549"/>
+  <dimension ref="A1:B552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21421,6 +21511,36 @@
       </c>
       <c r="B549" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>
@@ -21589,28 +21709,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.573973013476023</v>
+        <v>-2.5688302061067</v>
       </c>
       <c r="J2" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K2" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8938260744542753</v>
+        <v>0.8942338487812422</v>
       </c>
       <c r="M2" t="n">
-        <v>5.333977337516006</v>
+        <v>5.333904142640166</v>
       </c>
       <c r="N2" t="n">
-        <v>47.26701817134761</v>
+        <v>47.13642974479028</v>
       </c>
       <c r="O2" t="n">
-        <v>6.875101320805942</v>
+        <v>6.865597551909832</v>
       </c>
       <c r="P2" t="n">
-        <v>386.3969274065884</v>
+        <v>386.3424736377125</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21667,28 +21787,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.365294523949805</v>
+        <v>-2.355593853086691</v>
       </c>
       <c r="J3" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K3" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9109788871919831</v>
+        <v>0.9099984634303284</v>
       </c>
       <c r="M3" t="n">
-        <v>4.559258141589329</v>
+        <v>4.590199732555011</v>
       </c>
       <c r="N3" t="n">
-        <v>32.83526546262826</v>
+        <v>33.14365348735277</v>
       </c>
       <c r="O3" t="n">
-        <v>5.730206406633906</v>
+        <v>5.757052499964958</v>
       </c>
       <c r="P3" t="n">
-        <v>384.3950562343617</v>
+        <v>384.2923605222658</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21745,28 +21865,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.188167233804795</v>
+        <v>-2.181923561270403</v>
       </c>
       <c r="J4" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K4" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9193149304887456</v>
+        <v>0.9191218248019813</v>
       </c>
       <c r="M4" t="n">
-        <v>3.730781446944583</v>
+        <v>3.747443913376396</v>
       </c>
       <c r="N4" t="n">
-        <v>25.23918094168982</v>
+        <v>25.30041350942215</v>
       </c>
       <c r="O4" t="n">
-        <v>5.023861158679629</v>
+        <v>5.029951640863175</v>
       </c>
       <c r="P4" t="n">
-        <v>386.2051445445211</v>
+        <v>386.1390424278162</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21823,28 +21943,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.125849975212372</v>
+        <v>-2.119708575180505</v>
       </c>
       <c r="J5" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K5" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9336588808381172</v>
+        <v>0.933359949294517</v>
       </c>
       <c r="M5" t="n">
-        <v>3.170646185571604</v>
+        <v>3.185146195453572</v>
       </c>
       <c r="N5" t="n">
-        <v>19.28613303114364</v>
+        <v>19.37442227067817</v>
       </c>
       <c r="O5" t="n">
-        <v>4.39159800427403</v>
+        <v>4.401638589284468</v>
       </c>
       <c r="P5" t="n">
-        <v>387.3956985752966</v>
+        <v>387.33068183017</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21901,28 +22021,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.098100306819812</v>
+        <v>-2.094271148077923</v>
       </c>
       <c r="J6" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K6" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9344952903338324</v>
+        <v>0.9347129602338503</v>
       </c>
       <c r="M6" t="n">
-        <v>3.185711609787253</v>
+        <v>3.191630280375666</v>
       </c>
       <c r="N6" t="n">
-        <v>18.29182343536037</v>
+        <v>18.26186424273516</v>
       </c>
       <c r="O6" t="n">
-        <v>4.276894134224083</v>
+        <v>4.273390251631035</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9527248959201</v>
+        <v>384.9117936342624</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21979,28 +22099,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.899227672687966</v>
+        <v>-1.898549215923113</v>
       </c>
       <c r="J7" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K7" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L7" t="n">
-        <v>0.932828220155652</v>
+        <v>0.9334798722677754</v>
       </c>
       <c r="M7" t="n">
-        <v>2.799250874552045</v>
+        <v>2.787012190041446</v>
       </c>
       <c r="N7" t="n">
-        <v>15.61938031765035</v>
+        <v>15.53143727347983</v>
       </c>
       <c r="O7" t="n">
-        <v>3.952136171445811</v>
+        <v>3.940994452353343</v>
       </c>
       <c r="P7" t="n">
-        <v>381.2677497896391</v>
+        <v>381.2605663160164</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22038,7 +22158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H516"/>
+  <dimension ref="A1:H519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43701,6 +43821,132 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-41.153577385878414,176.02772932496632</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-41.153929303958144,176.02695848000715</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-41.15424024974694,176.0261607773832</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-41.154550226623236,176.02536244011077</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-41.15480681009307,176.02452910430856</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-41.155081377809374,176.0237075581648</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-41.15357698261842,176.0277290606217</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-41.15393148156884,176.02695990746048</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-41.154243314542434,176.02616278637817</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-41.15455167837324,176.02536339173352</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-41.154804148541984,176.02452735968163</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-41.155079442129185,176.02370628935512</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-41.15358875781001,176.02773677948616</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-41.153934143093004,176.02696165212578</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-41.154247750430535,176.02616569413436</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-41.154554178609324,176.0253650306395</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-41.15480672944,176.02452905144108</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-41.15508258760947,176.02370835117085</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0344/nzd0344.xlsx
+++ b/data/nzd0344/nzd0344.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H519"/>
+  <dimension ref="A1:H525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16004,6 +16004,186 @@
       <c r="H519" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>323.72</v>
+      </c>
+      <c r="C520" t="n">
+        <v>330.56</v>
+      </c>
+      <c r="D520" t="n">
+        <v>333.62</v>
+      </c>
+      <c r="E520" t="n">
+        <v>336.12</v>
+      </c>
+      <c r="F520" t="n">
+        <v>332.09</v>
+      </c>
+      <c r="G520" t="n">
+        <v>331.17</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>321.86</v>
+      </c>
+      <c r="C521" t="n">
+        <v>329.54</v>
+      </c>
+      <c r="D521" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="E521" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="F521" t="n">
+        <v>331.26</v>
+      </c>
+      <c r="G521" t="n">
+        <v>330.69</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:47+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>321.39</v>
+      </c>
+      <c r="C522" t="n">
+        <v>329.08</v>
+      </c>
+      <c r="D522" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="E522" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="F522" t="n">
+        <v>330.79</v>
+      </c>
+      <c r="G522" t="n">
+        <v>330</v>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:01:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>321.67</v>
+      </c>
+      <c r="C523" t="n">
+        <v>328.96</v>
+      </c>
+      <c r="D523" t="n">
+        <v>332.42</v>
+      </c>
+      <c r="E523" t="n">
+        <v>334.86</v>
+      </c>
+      <c r="F523" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="G523" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:41+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>322.1</v>
+      </c>
+      <c r="C524" t="n">
+        <v>328.18</v>
+      </c>
+      <c r="D524" t="n">
+        <v>331.04</v>
+      </c>
+      <c r="E524" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="F524" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="G524" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>322.25</v>
+      </c>
+      <c r="C525" t="n">
+        <v>328.04</v>
+      </c>
+      <c r="D525" t="n">
+        <v>330.89</v>
+      </c>
+      <c r="E525" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="F525" t="n">
+        <v>330.13</v>
+      </c>
+      <c r="G525" t="n">
+        <v>329.52</v>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B552"/>
+  <dimension ref="A1:B558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21541,6 +21721,66 @@
       </c>
       <c r="B552" t="n">
         <v>-0.03</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -21709,28 +21949,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.5688302061067</v>
+        <v>-2.558044828967631</v>
       </c>
       <c r="J2" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="K2" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8942338487812422</v>
+        <v>0.8948890566223577</v>
       </c>
       <c r="M2" t="n">
-        <v>5.333904142640166</v>
+        <v>5.337576812070869</v>
       </c>
       <c r="N2" t="n">
-        <v>47.13642974479028</v>
+        <v>46.91851369298181</v>
       </c>
       <c r="O2" t="n">
-        <v>6.865597551909832</v>
+        <v>6.849709022504665</v>
       </c>
       <c r="P2" t="n">
-        <v>386.3424736377125</v>
+        <v>386.2278797173755</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21787,28 +22027,28 @@
         <v>0.074</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.355593853086691</v>
+        <v>-2.338402635344612</v>
       </c>
       <c r="J3" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="K3" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9099984634303284</v>
+        <v>0.9086113801406525</v>
       </c>
       <c r="M3" t="n">
-        <v>4.590199732555011</v>
+        <v>4.640314125546698</v>
       </c>
       <c r="N3" t="n">
-        <v>33.14365348735277</v>
+        <v>33.57389573294914</v>
       </c>
       <c r="O3" t="n">
-        <v>5.757052499964958</v>
+        <v>5.794298554005406</v>
       </c>
       <c r="P3" t="n">
-        <v>384.2923605222658</v>
+        <v>384.1097116000961</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21865,28 +22105,28 @@
         <v>0.0703</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.181923561270403</v>
+        <v>-2.171535136204963</v>
       </c>
       <c r="J4" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="K4" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9191218248019813</v>
+        <v>0.9191703489131864</v>
       </c>
       <c r="M4" t="n">
-        <v>3.747443913376396</v>
+        <v>3.767418135234992</v>
       </c>
       <c r="N4" t="n">
-        <v>25.30041350942215</v>
+        <v>25.31381643688044</v>
       </c>
       <c r="O4" t="n">
-        <v>5.029951640863175</v>
+        <v>5.03128377622257</v>
       </c>
       <c r="P4" t="n">
-        <v>386.1390424278162</v>
+        <v>386.0286788826616</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21943,28 +22183,28 @@
         <v>0.0791</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.119708575180505</v>
+        <v>-2.109609213643663</v>
       </c>
       <c r="J5" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="K5" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.933359949294517</v>
+        <v>0.933226370063741</v>
       </c>
       <c r="M5" t="n">
-        <v>3.185146195453572</v>
+        <v>3.203170772078475</v>
       </c>
       <c r="N5" t="n">
-        <v>19.37442227067817</v>
+        <v>19.43887906623307</v>
       </c>
       <c r="O5" t="n">
-        <v>4.401638589284468</v>
+        <v>4.40895441870667</v>
       </c>
       <c r="P5" t="n">
-        <v>387.33068183017</v>
+        <v>387.2233890506853</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22021,28 +22261,28 @@
         <v>0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.094271148077923</v>
+        <v>-2.089101468216194</v>
       </c>
       <c r="J6" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="K6" t="n">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9347129602338503</v>
+        <v>0.9355129352595669</v>
       </c>
       <c r="M6" t="n">
-        <v>3.191630280375666</v>
+        <v>3.187700508177002</v>
       </c>
       <c r="N6" t="n">
-        <v>18.26186424273516</v>
+        <v>18.12855057335326</v>
       </c>
       <c r="O6" t="n">
-        <v>4.273390251631035</v>
+        <v>4.257763564754772</v>
       </c>
       <c r="P6" t="n">
-        <v>384.9117936342624</v>
+        <v>384.8563455145415</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22099,28 +22339,28 @@
         <v>0.1269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.898549215923113</v>
+        <v>-1.897978146402494</v>
       </c>
       <c r="J7" t="n">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="K7" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9334798722677754</v>
+        <v>0.9347931528145667</v>
       </c>
       <c r="M7" t="n">
-        <v>2.787012190041446</v>
+        <v>2.760055181440733</v>
       </c>
       <c r="N7" t="n">
-        <v>15.53143727347983</v>
+        <v>15.35747422585021</v>
       </c>
       <c r="O7" t="n">
-        <v>3.940994452353343</v>
+        <v>3.918861343024299</v>
       </c>
       <c r="P7" t="n">
-        <v>381.2605663160164</v>
+        <v>381.2545103727601</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22158,7 +22398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H519"/>
+  <dimension ref="A1:H525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43947,6 +44187,258 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:54:39+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-41.153595774533464,176.02774137908483</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-41.153936804617125,176.02696339679122</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-41.15424734716799,176.02616542979288</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-41.154553372081544,176.02536450196015</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-41.15480672944,176.02452905144108</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-41.15508516851634,176.0237100429173</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-41.15358077326235,176.0277315454613</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-41.15392857808789,176.02695800418937</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-41.1542412175771,176.02616141180266</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-41.154551597720456,176.02536333886562</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-41.15480003523571,176.02452466344025</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-41.15508129715602,176.02370750529772</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:47+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-41.15357698261842,176.0277290606217</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-41.15392486808442,176.02695557223217</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-41.15423912061175,176.0261600372272</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-41.154547565081536,176.02536069546915</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-41.154796244541615,176.0245221786691</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-41.15507573207546,176.02370385747014</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:01:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-41.1535792408744,176.02773054095167</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-41.1539239002574,176.02695493780857</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-41.1542376688665,176.02615908559812</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-41.15454320983143,176.02535784060134</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-41.154791244051445,176.02451890088633</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-41.155074119008596,176.02370280012894</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:41+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-41.15358270891031,176.02773281431573</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-41.15391760938177,176.0269508140558</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-41.15422653881927,176.02615178977655</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-41.15453457998373,176.02535218373484</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-41.154791244051445,176.02451890088633</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-41.155074119008596,176.02370280012894</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-41.15358391869025,176.02773360734972</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-41.153916480250224,176.0269500738951</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-41.15422532903149,176.02615099675262</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-41.154534176719814,176.02535191939532</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-41.154790921439165,176.02451868941648</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-41.15507186071498,176.02370131985134</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
